--- a/research/traditional_assets/database/data/spain/spain_retail_general.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_retail_general.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0555</v>
+        <v>-0.0461</v>
       </c>
       <c r="G2">
-        <v>0.01683259776249615</v>
+        <v>0.01806257836072801</v>
       </c>
       <c r="H2">
-        <v>0.01683259776249615</v>
+        <v>0.01806257836072801</v>
       </c>
       <c r="I2">
-        <v>-0.009941656880471657</v>
+        <v>-0.009383281974769449</v>
       </c>
       <c r="J2">
-        <v>-0.009941656880471657</v>
+        <v>-0.009383281974769449</v>
       </c>
       <c r="K2">
-        <v>-333</v>
+        <v>-268.9</v>
       </c>
       <c r="L2">
-        <v>-0.04272298060145746</v>
+        <v>-0.03704826331960154</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.496</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.0006296813507680589</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.00184455187802157</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,76 +627,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.496</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>291.2</v>
+        <v>342.9</v>
       </c>
       <c r="V2">
-        <v>0.2785803118721898</v>
+        <v>0.4353180144725148</v>
       </c>
       <c r="W2">
-        <v>0.5809490579204466</v>
+        <v>0.2888602427758084</v>
       </c>
       <c r="X2">
-        <v>0.1544305280441174</v>
+        <v>0.1895902016424064</v>
       </c>
       <c r="Y2">
-        <v>0.4265185298763292</v>
+        <v>0.09927004113340193</v>
       </c>
       <c r="Z2">
-        <v>7.779647827669601</v>
+        <v>8.892834185924604</v>
       </c>
       <c r="AA2">
-        <v>-0.07734258935359788</v>
+        <v>-0.0834439707213999</v>
       </c>
       <c r="AB2">
-        <v>0.06801499009019375</v>
+        <v>0.1035112596254378</v>
       </c>
       <c r="AC2">
-        <v>-0.1453575794437916</v>
+        <v>-0.1869552303468378</v>
       </c>
       <c r="AD2">
-        <v>2607.4</v>
+        <v>1421.3</v>
       </c>
       <c r="AE2">
-        <v>5.796251945741328</v>
+        <v>3.373994505370716</v>
       </c>
       <c r="AF2">
-        <v>2613.196251945742</v>
+        <v>1424.673994505371</v>
       </c>
       <c r="AG2">
-        <v>2321.996251945742</v>
+        <v>1081.773994505371</v>
       </c>
       <c r="AH2">
-        <v>0.7142815167723445</v>
+        <v>0.6439571239056671</v>
       </c>
       <c r="AI2">
-        <v>1.553350813760253</v>
+        <v>0.979309500916509</v>
       </c>
       <c r="AJ2">
-        <v>0.6895729030684518</v>
+        <v>0.5786515338992928</v>
       </c>
       <c r="AK2">
-        <v>1.669184464193574</v>
+        <v>0.9729285870982258</v>
       </c>
       <c r="AL2">
-        <v>121.7</v>
+        <v>102.6</v>
       </c>
       <c r="AM2">
-        <v>116.1</v>
+        <v>81.89999999999999</v>
       </c>
       <c r="AN2">
-        <v>24.17168814313526</v>
+        <v>14.52232553387146</v>
       </c>
       <c r="AO2">
-        <v>-0.6647493837304849</v>
+        <v>-0.6842105263157895</v>
       </c>
       <c r="AP2">
-        <v>21.5258760725479</v>
+        <v>11.05317251972383</v>
       </c>
       <c r="AQ2">
-        <v>-0.6968130921619293</v>
+        <v>-0.8571428571428573</v>
       </c>
     </row>
     <row r="3">
@@ -716,34 +719,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0555</v>
+        <v>-0.0461</v>
       </c>
       <c r="G3">
-        <v>0.01683259776249615</v>
+        <v>0.01806257836072801</v>
       </c>
       <c r="H3">
-        <v>0.01683259776249615</v>
+        <v>0.01806257836072801</v>
       </c>
       <c r="I3">
-        <v>-0.009941656880471657</v>
+        <v>-0.009383281974769449</v>
       </c>
       <c r="J3">
-        <v>-0.009941656880471657</v>
+        <v>-0.009383281974769449</v>
       </c>
       <c r="K3">
-        <v>-333</v>
+        <v>-268.9</v>
       </c>
       <c r="L3">
-        <v>-0.04272298060145746</v>
+        <v>-0.03704826331960154</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.496</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0006296813507680589</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.00184455187802157</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,76 +758,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.496</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>291.2</v>
+        <v>342.9</v>
       </c>
       <c r="V3">
-        <v>0.2785803118721898</v>
+        <v>0.4353180144725148</v>
       </c>
       <c r="W3">
-        <v>0.5809490579204466</v>
+        <v>0.2888602427758084</v>
       </c>
       <c r="X3">
-        <v>0.1544305280441174</v>
+        <v>0.1895902016424064</v>
       </c>
       <c r="Y3">
-        <v>0.4265185298763292</v>
+        <v>0.09927004113340193</v>
       </c>
       <c r="Z3">
-        <v>7.779647827669601</v>
+        <v>8.892834185924604</v>
       </c>
       <c r="AA3">
-        <v>-0.07734258935359788</v>
+        <v>-0.0834439707213999</v>
       </c>
       <c r="AB3">
-        <v>0.06801499009019375</v>
+        <v>0.1035112596254378</v>
       </c>
       <c r="AC3">
-        <v>-0.1453575794437916</v>
+        <v>-0.1869552303468378</v>
       </c>
       <c r="AD3">
-        <v>2607.4</v>
+        <v>1421.3</v>
       </c>
       <c r="AE3">
-        <v>5.796251945741328</v>
+        <v>3.373994505370716</v>
       </c>
       <c r="AF3">
-        <v>2613.196251945742</v>
+        <v>1424.673994505371</v>
       </c>
       <c r="AG3">
-        <v>2321.996251945742</v>
+        <v>1081.773994505371</v>
       </c>
       <c r="AH3">
-        <v>0.7142815167723445</v>
+        <v>0.6439571239056671</v>
       </c>
       <c r="AI3">
-        <v>1.553350813760253</v>
+        <v>0.979309500916509</v>
       </c>
       <c r="AJ3">
-        <v>0.6895729030684518</v>
+        <v>0.5786515338992928</v>
       </c>
       <c r="AK3">
-        <v>1.669184464193574</v>
+        <v>0.9729285870982258</v>
       </c>
       <c r="AL3">
-        <v>121.7</v>
+        <v>102.6</v>
       </c>
       <c r="AM3">
-        <v>116.1</v>
+        <v>81.89999999999999</v>
       </c>
       <c r="AN3">
-        <v>24.17168814313526</v>
+        <v>14.52232553387146</v>
       </c>
       <c r="AO3">
-        <v>-0.6647493837304849</v>
+        <v>-0.6842105263157895</v>
       </c>
       <c r="AP3">
-        <v>21.5258760725479</v>
+        <v>11.05317251972383</v>
       </c>
       <c r="AQ3">
-        <v>-0.6968130921619293</v>
+        <v>-0.8571428571428573</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/spain/spain_retail_general.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_retail_general.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0461</v>
+        <v>-0.0276</v>
       </c>
       <c r="G2">
-        <v>0.01806257836072801</v>
+        <v>0.01942460722301571</v>
       </c>
       <c r="H2">
-        <v>0.01806257836072801</v>
+        <v>0.01942460722301571</v>
       </c>
       <c r="I2">
-        <v>-0.009383281974769449</v>
+        <v>-0.001775461957235982</v>
       </c>
       <c r="J2">
-        <v>-0.009383281974769449</v>
+        <v>-0.001775461957235982</v>
       </c>
       <c r="K2">
-        <v>-268.9</v>
+        <v>-94.3</v>
       </c>
       <c r="L2">
-        <v>-0.03704826331960154</v>
+        <v>-0.0128273141535741</v>
       </c>
       <c r="M2">
-        <v>0.496</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.0006296813507680589</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.00184455187802157</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +627,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.496</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>342.9</v>
+        <v>170.9</v>
       </c>
       <c r="V2">
-        <v>0.4353180144725148</v>
+        <v>0.2257595772787318</v>
       </c>
       <c r="W2">
-        <v>0.2888602427758084</v>
+        <v>-3.132890365448505</v>
       </c>
       <c r="X2">
-        <v>0.1895902016424064</v>
+        <v>0.1799838389223679</v>
       </c>
       <c r="Y2">
-        <v>0.09927004113340193</v>
+        <v>-3.312874204370873</v>
       </c>
       <c r="Z2">
-        <v>8.892834185924604</v>
+        <v>11.49818921972468</v>
       </c>
       <c r="AA2">
-        <v>-0.0834439707213999</v>
+        <v>-0.02041459753672204</v>
       </c>
       <c r="AB2">
-        <v>0.1035112596254378</v>
+        <v>0.1002838547024031</v>
       </c>
       <c r="AC2">
-        <v>-0.1869552303468378</v>
+        <v>-0.1206984522391251</v>
       </c>
       <c r="AD2">
-        <v>1421.3</v>
+        <v>1126.5</v>
       </c>
       <c r="AE2">
-        <v>3.373994505370716</v>
+        <v>2.461542893101588</v>
       </c>
       <c r="AF2">
-        <v>1424.673994505371</v>
+        <v>1128.961542893102</v>
       </c>
       <c r="AG2">
-        <v>1081.773994505371</v>
+        <v>958.0615428931015</v>
       </c>
       <c r="AH2">
-        <v>0.6439571239056671</v>
+        <v>0.5986132363872344</v>
       </c>
       <c r="AI2">
-        <v>0.979309500916509</v>
+        <v>1.052191991754899</v>
       </c>
       <c r="AJ2">
-        <v>0.5786515338992928</v>
+        <v>0.5586164221704648</v>
       </c>
       <c r="AK2">
-        <v>0.9729285870982258</v>
+        <v>1.062080021525357</v>
       </c>
       <c r="AL2">
-        <v>102.6</v>
+        <v>111.7</v>
       </c>
       <c r="AM2">
-        <v>81.89999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="AN2">
-        <v>14.52232553387146</v>
+        <v>7.047672672672673</v>
       </c>
       <c r="AO2">
-        <v>-0.6842105263157895</v>
+        <v>-0.1298119964189794</v>
       </c>
       <c r="AP2">
-        <v>11.05317251972383</v>
+        <v>5.993878521603488</v>
       </c>
       <c r="AQ2">
-        <v>-0.8571428571428573</v>
+        <v>-0.2065527065527065</v>
       </c>
     </row>
     <row r="3">
@@ -719,34 +716,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0461</v>
+        <v>-0.0276</v>
       </c>
       <c r="G3">
-        <v>0.01806257836072801</v>
+        <v>0.01942460722301571</v>
       </c>
       <c r="H3">
-        <v>0.01806257836072801</v>
+        <v>0.01942460722301571</v>
       </c>
       <c r="I3">
-        <v>-0.009383281974769449</v>
+        <v>-0.001775461957235982</v>
       </c>
       <c r="J3">
-        <v>-0.009383281974769449</v>
+        <v>-0.001775461957235982</v>
       </c>
       <c r="K3">
-        <v>-268.9</v>
+        <v>-94.3</v>
       </c>
       <c r="L3">
-        <v>-0.03704826331960154</v>
+        <v>-0.0128273141535741</v>
       </c>
       <c r="M3">
-        <v>0.496</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.0006296813507680589</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.00184455187802157</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +755,76 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0.496</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>342.9</v>
+        <v>170.9</v>
       </c>
       <c r="V3">
-        <v>0.4353180144725148</v>
+        <v>0.2257595772787318</v>
       </c>
       <c r="W3">
-        <v>0.2888602427758084</v>
+        <v>-3.132890365448505</v>
       </c>
       <c r="X3">
-        <v>0.1895902016424064</v>
+        <v>0.1799838389223679</v>
       </c>
       <c r="Y3">
-        <v>0.09927004113340193</v>
+        <v>-3.312874204370873</v>
       </c>
       <c r="Z3">
-        <v>8.892834185924604</v>
+        <v>11.49818921972468</v>
       </c>
       <c r="AA3">
-        <v>-0.0834439707213999</v>
+        <v>-0.02041459753672204</v>
       </c>
       <c r="AB3">
-        <v>0.1035112596254378</v>
+        <v>0.1002838547024031</v>
       </c>
       <c r="AC3">
-        <v>-0.1869552303468378</v>
+        <v>-0.1206984522391251</v>
       </c>
       <c r="AD3">
-        <v>1421.3</v>
+        <v>1126.5</v>
       </c>
       <c r="AE3">
-        <v>3.373994505370716</v>
+        <v>2.461542893101588</v>
       </c>
       <c r="AF3">
-        <v>1424.673994505371</v>
+        <v>1128.961542893102</v>
       </c>
       <c r="AG3">
-        <v>1081.773994505371</v>
+        <v>958.0615428931015</v>
       </c>
       <c r="AH3">
-        <v>0.6439571239056671</v>
+        <v>0.5986132363872344</v>
       </c>
       <c r="AI3">
-        <v>0.979309500916509</v>
+        <v>1.052191991754899</v>
       </c>
       <c r="AJ3">
-        <v>0.5786515338992928</v>
+        <v>0.5586164221704648</v>
       </c>
       <c r="AK3">
-        <v>0.9729285870982258</v>
+        <v>1.062080021525357</v>
       </c>
       <c r="AL3">
-        <v>102.6</v>
+        <v>111.7</v>
       </c>
       <c r="AM3">
-        <v>81.89999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="AN3">
-        <v>14.52232553387146</v>
+        <v>7.047672672672673</v>
       </c>
       <c r="AO3">
-        <v>-0.6842105263157895</v>
+        <v>-0.1298119964189794</v>
       </c>
       <c r="AP3">
-        <v>11.05317251972383</v>
+        <v>5.993878521603488</v>
       </c>
       <c r="AQ3">
-        <v>-0.8571428571428573</v>
+        <v>-0.2065527065527065</v>
       </c>
     </row>
   </sheetData>
